--- a/research/traditional_assets/database/data/poland/poland_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0223</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.0313</v>
+        <v>-0.00513</v>
       </c>
       <c r="F2">
-        <v>1.035</v>
+        <v>0.104</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1056.6</v>
+        <v>698.3</v>
       </c>
       <c r="L2">
-        <v>0.08994943217611903</v>
+        <v>0.05821980623968252</v>
       </c>
       <c r="M2">
-        <v>418.228</v>
+        <v>1019.0924</v>
       </c>
       <c r="N2">
-        <v>0.007856171434153085</v>
+        <v>0.03181601458596101</v>
       </c>
       <c r="O2">
-        <v>0.3958243422297937</v>
+        <v>1.459390519833882</v>
       </c>
       <c r="P2">
-        <v>418.228</v>
+        <v>1019.0924</v>
       </c>
       <c r="Q2">
-        <v>0.007856171434153085</v>
+        <v>0.03181601458596101</v>
       </c>
       <c r="R2">
-        <v>0.3958243422297937</v>
+        <v>1.459390519833882</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>15271.1</v>
+        <v>14961.2</v>
       </c>
       <c r="V2">
-        <v>0.2868587937395277</v>
+        <v>0.4670879278694257</v>
       </c>
       <c r="W2">
-        <v>0.03622813075506446</v>
+        <v>0.05016126698235721</v>
       </c>
       <c r="X2">
-        <v>0.05859193473351169</v>
+        <v>0.1045078533192682</v>
       </c>
       <c r="Y2">
-        <v>-0.02236380397844723</v>
+        <v>-0.05434658633691103</v>
       </c>
       <c r="Z2">
-        <v>0.1585293717140339</v>
+        <v>0.1862189413208966</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0467698825882807</v>
+        <v>0.07552540208701625</v>
       </c>
       <c r="AC2">
-        <v>-0.0467698825882807</v>
+        <v>-0.07552540208701625</v>
       </c>
       <c r="AD2">
-        <v>37777.12</v>
+        <v>38818.526</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>37777.12</v>
+        <v>38818.526</v>
       </c>
       <c r="AG2">
-        <v>22506.02</v>
+        <v>23857.326</v>
       </c>
       <c r="AH2">
-        <v>0.4150751675150463</v>
+        <v>0.5479025446198317</v>
       </c>
       <c r="AI2">
-        <v>0.4741168680499183</v>
+        <v>0.6083118804624587</v>
       </c>
       <c r="AJ2">
-        <v>0.2971420468693435</v>
+        <v>0.4268764710414516</v>
       </c>
       <c r="AK2">
-        <v>0.3494299294712971</v>
+        <v>0.4883559894364088</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -712,26 +712,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.229</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
-        <v>-71.2</v>
-      </c>
-      <c r="L3">
-        <v>-0.8240740740740741</v>
+        <v>-42.8</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,55 +737,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>53.3</v>
+        <v>43.5</v>
       </c>
       <c r="V3">
-        <v>0.895798319327731</v>
+        <v>2.004608294930875</v>
       </c>
       <c r="W3">
-        <v>-0.3491907797940167</v>
+        <v>-0.2458357265939115</v>
       </c>
       <c r="X3">
-        <v>0.04689551976079166</v>
+        <v>0.07164542988177777</v>
       </c>
       <c r="Y3">
-        <v>-0.3960862995548083</v>
+        <v>-0.3174811564756893</v>
       </c>
       <c r="Z3">
-        <v>-0.4632707774798928</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04466207318927493</v>
+        <v>0.07155519558247968</v>
       </c>
       <c r="AC3">
-        <v>-0.04466207318927493</v>
+        <v>-0.07155519558247968</v>
       </c>
       <c r="AD3">
-        <v>8.220000000000001</v>
+        <v>0.126</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.220000000000001</v>
+        <v>0.126</v>
       </c>
       <c r="AG3">
-        <v>-45.08</v>
+        <v>-43.374</v>
       </c>
       <c r="AH3">
-        <v>0.1213821618428825</v>
+        <v>0.005772931366260423</v>
       </c>
       <c r="AI3">
-        <v>0.04330418291012539</v>
+        <v>0.00285545936635997</v>
       </c>
       <c r="AJ3">
-        <v>-3.126213592233009</v>
+        <v>2.001199593983574</v>
       </c>
       <c r="AK3">
-        <v>-0.3302080281277469</v>
+        <v>-69.2875399361025</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,10 +811,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0891</v>
+        <v>0.0929</v>
       </c>
       <c r="E4">
-        <v>0.102</v>
+        <v>0.0587</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,28 +829,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>492</v>
+        <v>347</v>
       </c>
       <c r="L4">
-        <v>0.3233013536601393</v>
+        <v>0.2612558349646137</v>
       </c>
       <c r="M4">
-        <v>166.528</v>
+        <v>273.4</v>
       </c>
       <c r="N4">
-        <v>0.01942629166034786</v>
+        <v>0.05583352053423734</v>
       </c>
       <c r="O4">
-        <v>0.3384715447154472</v>
+        <v>0.7878962536023054</v>
       </c>
       <c r="P4">
-        <v>166.528</v>
+        <v>273.4</v>
       </c>
       <c r="Q4">
-        <v>0.01942629166034786</v>
+        <v>0.05583352053423734</v>
       </c>
       <c r="R4">
-        <v>0.3384715447154472</v>
+        <v>0.7878962536023054</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -877,55 +859,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>331.9</v>
+        <v>378.1</v>
       </c>
       <c r="V4">
-        <v>0.03871773036407965</v>
+        <v>0.07721526742500052</v>
       </c>
       <c r="W4">
-        <v>0.1021191805558438</v>
+        <v>0.07898031182428587</v>
       </c>
       <c r="X4">
-        <v>0.05156763450038149</v>
+        <v>0.08717260094146112</v>
       </c>
       <c r="Y4">
-        <v>0.05055154605546236</v>
+        <v>-0.008192289117175247</v>
       </c>
       <c r="Z4">
-        <v>0.2380602268283145</v>
+        <v>0.1904229390681004</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04476647806294864</v>
+        <v>0.07211964660397922</v>
       </c>
       <c r="AC4">
-        <v>-0.04476647806294864</v>
+        <v>-0.07211964660397922</v>
       </c>
       <c r="AD4">
-        <v>2913.4</v>
+        <v>2899.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2913.4</v>
+        <v>2899.7</v>
       </c>
       <c r="AG4">
-        <v>2581.5</v>
+        <v>2521.6</v>
       </c>
       <c r="AH4">
-        <v>0.2536545443464482</v>
+        <v>0.3719280693653481</v>
       </c>
       <c r="AI4">
-        <v>0.3987190190094295</v>
+        <v>0.6590976247300829</v>
       </c>
       <c r="AJ4">
-        <v>0.2314457852929047</v>
+        <v>0.3399161532965774</v>
       </c>
       <c r="AK4">
-        <v>0.3701075268817204</v>
+        <v>0.627045307604317</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -942,7 +924,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank Millennium S.A. (WSE:MIL)</t>
+          <t>Powszechna Kasa Oszczednosci Bank Polski Spólka Akcyjna (WSE:PKO)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -951,10 +933,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0784</v>
-      </c>
-      <c r="F5">
-        <v>2.66</v>
+        <v>0.0582</v>
+      </c>
+      <c r="E5">
+        <v>-0.00513</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,82 +951,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-234.8</v>
+        <v>566.6</v>
       </c>
       <c r="L5">
-        <v>-0.2726111691628934</v>
+        <v>0.1994017244413162</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>462.3</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.0534623924507355</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.8159195199435227</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>462.3</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.0534623924507355</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.8159195199435227</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>481.1</v>
+        <v>2766.7</v>
       </c>
       <c r="V5">
-        <v>0.1960952148039455</v>
+        <v>0.3199532796743454</v>
       </c>
       <c r="W5">
-        <v>-0.09827146026032729</v>
+        <v>0.05413565443375405</v>
       </c>
       <c r="X5">
-        <v>0.05014188327412533</v>
+        <v>0.103141691316312</v>
       </c>
       <c r="Y5">
-        <v>-0.1484133435344526</v>
+        <v>-0.04900603688255793</v>
       </c>
       <c r="Z5">
-        <v>0.2695605908863294</v>
+        <v>0.1340545181774435</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0454291034054831</v>
+        <v>0.0724109658954671</v>
       </c>
       <c r="AC5">
-        <v>-0.0454291034054831</v>
+        <v>-0.0724109658954671</v>
       </c>
       <c r="AD5">
-        <v>682.8</v>
+        <v>10335.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>682.8</v>
+        <v>10335.4</v>
       </c>
       <c r="AG5">
-        <v>201.6999999999999</v>
+        <v>7568.7</v>
       </c>
       <c r="AH5">
-        <v>0.2177157069064473</v>
+        <v>0.5444670382350153</v>
       </c>
       <c r="AI5">
-        <v>0.2535744791473242</v>
+        <v>0.6174701134523817</v>
       </c>
       <c r="AJ5">
-        <v>0.07596700689239574</v>
+        <v>0.4667456015392299</v>
       </c>
       <c r="AK5">
-        <v>0.09120094049556879</v>
+        <v>0.5417203469896076</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1061,7 +1046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bank Handlowy w Warszawie S.A. (WSE:BHW)</t>
+          <t>Santander Bank Polska S.A. (WSE:SPL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1070,10 +1055,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0207</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="E6">
-        <v>-0.0313</v>
+        <v>-0.00338</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1088,28 +1073,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>126.7</v>
+        <v>422.2</v>
       </c>
       <c r="L6">
-        <v>0.2195840554592721</v>
+        <v>0.1992731391891254</v>
       </c>
       <c r="M6">
-        <v>39.5</v>
+        <v>55.3924</v>
       </c>
       <c r="N6">
-        <v>0.0207632464255677</v>
+        <v>0.009149719193921374</v>
       </c>
       <c r="O6">
-        <v>0.3117600631412786</v>
+        <v>0.1311994315490289</v>
       </c>
       <c r="P6">
-        <v>39.5</v>
+        <v>55.3924</v>
       </c>
       <c r="Q6">
-        <v>0.0207632464255677</v>
+        <v>0.009149719193921374</v>
       </c>
       <c r="R6">
-        <v>0.3117600631412786</v>
+        <v>0.1311994315490289</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1118,55 +1103,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3762.7</v>
+        <v>623.9</v>
       </c>
       <c r="V6">
-        <v>1.977870058873002</v>
+        <v>0.1030558308556326</v>
       </c>
       <c r="W6">
-        <v>0.06450463292943692</v>
+        <v>0.06143950638842807</v>
       </c>
       <c r="X6">
-        <v>0.0630167048030916</v>
+        <v>0.1058740153222245</v>
       </c>
       <c r="Y6">
-        <v>0.001487928126345323</v>
+        <v>-0.04443450893379643</v>
       </c>
       <c r="Z6">
-        <v>0.199364245732845</v>
+        <v>0.18636255684467</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04561563267450859</v>
+        <v>0.07244549486119684</v>
       </c>
       <c r="AC6">
-        <v>-0.04561563267450859</v>
+        <v>-0.07244549486119684</v>
       </c>
       <c r="AD6">
-        <v>1586.9</v>
+        <v>7860.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1586.9</v>
+        <v>7860.6</v>
       </c>
       <c r="AG6">
-        <v>-2175.8</v>
+        <v>7236.700000000001</v>
       </c>
       <c r="AH6">
-        <v>0.4547903590978133</v>
+        <v>0.5649174248630935</v>
       </c>
       <c r="AI6">
-        <v>0.4557307371988168</v>
+        <v>0.5742232871408639</v>
       </c>
       <c r="AJ6">
-        <v>7.958302852962702</v>
+        <v>0.5444935180238814</v>
       </c>
       <c r="AK6">
-        <v>7.754098360655745</v>
+        <v>0.5538912530998378</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1183,7 +1168,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Powszechna Kasa Oszczednosci Bank Polski Spólka Akcyjna (WSE:PKO)</t>
+          <t>Bank Millennium S.A. (WSE:MIL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1192,7 +1177,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.079</v>
+        <v>0.156</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1207,10 +1192,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-227.7</v>
+        <v>-358.1</v>
       </c>
       <c r="L7">
-        <v>-0.1355195810022616</v>
+        <v>-0.3711265416105296</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1234,55 +1219,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>998.8</v>
+        <v>2018.4</v>
       </c>
       <c r="V7">
-        <v>0.07206453195572808</v>
+        <v>1.590669083458113</v>
       </c>
       <c r="W7">
-        <v>-0.01962254395036194</v>
+        <v>-0.1781680680630877</v>
       </c>
       <c r="X7">
-        <v>0.06329721970156928</v>
+        <v>0.08801131286817385</v>
       </c>
       <c r="Y7">
-        <v>-0.08291976365193122</v>
+        <v>-0.2661793809312616</v>
       </c>
       <c r="Z7">
-        <v>0.07519355560528082</v>
+        <v>0.4362904684391391</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04563073131817982</v>
+        <v>0.07453645262697177</v>
       </c>
       <c r="AC7">
-        <v>-0.04563073131817982</v>
+        <v>-0.07453645262697177</v>
       </c>
       <c r="AD7">
-        <v>11729.1</v>
+        <v>791.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>11729.1</v>
+        <v>791.6</v>
       </c>
       <c r="AG7">
-        <v>10730.3</v>
+        <v>-1226.8</v>
       </c>
       <c r="AH7">
-        <v>0.458366713692265</v>
+        <v>0.3841785974278088</v>
       </c>
       <c r="AI7">
-        <v>0.5285259168803313</v>
+        <v>0.4460472192483236</v>
       </c>
       <c r="AJ7">
-        <v>0.4363666678866699</v>
+        <v>-29.14014251781479</v>
       </c>
       <c r="AK7">
-        <v>0.5063062382922905</v>
+        <v>5.034058268362738</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1299,7 +1284,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Santander Bank Polska S.A. (WSE:SPL)</t>
+          <t>Bank Ochrony Srodowiska S.A. (WSE:BOS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1308,13 +1293,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0223</v>
-      </c>
-      <c r="E8">
-        <v>-0.128</v>
-      </c>
-      <c r="F8">
-        <v>0.39</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1329,10 +1308,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>251.8</v>
+        <v>27.1</v>
       </c>
       <c r="L8">
-        <v>0.1347749290799122</v>
+        <v>0.2135539795114263</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1356,55 +1335,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>599.4</v>
+        <v>43.5</v>
       </c>
       <c r="V8">
-        <v>0.06820198894021801</v>
+        <v>0.2428810720268007</v>
       </c>
       <c r="W8">
-        <v>0.03622813075506446</v>
+        <v>0.0560264626834815</v>
       </c>
       <c r="X8">
-        <v>0.05826364059850019</v>
+        <v>0.1173109432693479</v>
       </c>
       <c r="Y8">
-        <v>-0.02203550984343573</v>
+        <v>-0.06128448058586642</v>
       </c>
       <c r="Z8">
-        <v>0.1533631035445158</v>
+        <v>0.1506589101270331</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.0467698825882807</v>
+        <v>0.07651435154706071</v>
       </c>
       <c r="AC8">
-        <v>-0.0467698825882807</v>
+        <v>-0.07651435154706071</v>
       </c>
       <c r="AD8">
-        <v>5527.6</v>
+        <v>309.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>5527.6</v>
+        <v>309.9</v>
       </c>
       <c r="AG8">
-        <v>4928.200000000001</v>
+        <v>266.4</v>
       </c>
       <c r="AH8">
-        <v>0.3861080454310502</v>
+        <v>0.6337423312883436</v>
       </c>
       <c r="AI8">
-        <v>0.430833982852689</v>
+        <v>0.4432842225718782</v>
       </c>
       <c r="AJ8">
-        <v>0.3592820482911466</v>
+        <v>0.5979797979797979</v>
       </c>
       <c r="AK8">
-        <v>0.4029401664677122</v>
+        <v>0.4063453325198292</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1421,7 +1400,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bank Polska Kasa Opieki S.A. (WSE:PEO)</t>
+          <t>BNP Paribas Bank Polska S.A. (WSE:BNP)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1430,13 +1409,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0104</v>
-      </c>
-      <c r="E9">
-        <v>-0.0561</v>
-      </c>
-      <c r="F9">
-        <v>0.3</v>
+        <v>0.149</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1451,85 +1424,82 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>419.7</v>
+        <v>-17.1</v>
       </c>
       <c r="L9">
-        <v>0.2310105680317041</v>
+        <v>-0.01807037937229209</v>
       </c>
       <c r="M9">
-        <v>212.2</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.02685328136468325</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.5055992375506314</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>212.2</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.02685328136468325</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.5055992375506314</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>2239.9</v>
+        <v>2227.5</v>
       </c>
       <c r="V9">
-        <v>0.2834527093720736</v>
+        <v>1.18006993006993</v>
       </c>
       <c r="W9">
-        <v>0.06444035006909259</v>
+        <v>-0.005569488323616585</v>
       </c>
       <c r="X9">
-        <v>0.05859193473351169</v>
+        <v>0.1182613938851505</v>
       </c>
       <c r="Y9">
-        <v>0.005848415335580899</v>
+        <v>-0.1238308822087671</v>
       </c>
       <c r="Z9">
-        <v>0.1837768943647013</v>
+        <v>0.1869493065707851</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04717222011447145</v>
+        <v>0.076552015978465</v>
       </c>
       <c r="AC9">
-        <v>-0.04717222011447145</v>
+        <v>-0.076552015978465</v>
       </c>
       <c r="AD9">
-        <v>5082.1</v>
+        <v>3333.9</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>5082.1</v>
+        <v>3333.9</v>
       </c>
       <c r="AG9">
-        <v>2842.2</v>
+        <v>1106.4</v>
       </c>
       <c r="AH9">
-        <v>0.391403464183668</v>
+        <v>0.6384946854352198</v>
       </c>
       <c r="AI9">
-        <v>0.4465974199444621</v>
+        <v>0.6029951708296407</v>
       </c>
       <c r="AJ9">
-        <v>0.2645284985666952</v>
+        <v>0.3695390781563127</v>
       </c>
       <c r="AK9">
-        <v>0.310973007866779</v>
+        <v>0.335130550675471</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1546,7 +1516,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BNP Paribas Bank Polska S.A. (WSE:BNP)</t>
+          <t>Bank Polska Kasa Opieki S.A. (WSE:PEO)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1555,10 +1525,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.142</v>
+        <v>0.0544</v>
       </c>
       <c r="E10">
-        <v>0.8320000000000001</v>
+        <v>-0.0446</v>
+      </c>
+      <c r="F10">
+        <v>0.104</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1573,82 +1546,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>155.5</v>
+        <v>308.2</v>
       </c>
       <c r="L10">
-        <v>0.1359622278569555</v>
+        <v>0.179520037278658</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>228</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.04397130293913446</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.7397793640493187</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>228</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.04397130293913446</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.7397793640493187</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>1180.2</v>
+        <v>2145.6</v>
       </c>
       <c r="V10">
-        <v>0.3554712207463631</v>
+        <v>0.4137931034482759</v>
       </c>
       <c r="W10">
-        <v>0.05077551020408163</v>
+        <v>0.04896338072920804</v>
       </c>
       <c r="X10">
-        <v>0.06582273425066199</v>
+        <v>0.1154768223111183</v>
       </c>
       <c r="Y10">
-        <v>-0.01504722404658036</v>
+        <v>-0.0665134415819103</v>
       </c>
       <c r="Z10">
-        <v>0.2231000312109863</v>
+        <v>0.1918619595221332</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04758571019684731</v>
+        <v>0.07739945471849607</v>
       </c>
       <c r="AC10">
-        <v>-0.04758571019684731</v>
+        <v>-0.07739945471849607</v>
       </c>
       <c r="AD10">
-        <v>3171.7</v>
+        <v>8612.9</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>3171.7</v>
+        <v>8612.9</v>
       </c>
       <c r="AG10">
-        <v>1991.5</v>
+        <v>6467.299999999999</v>
       </c>
       <c r="AH10">
-        <v>0.4885701962475739</v>
+        <v>0.6242091302425696</v>
       </c>
       <c r="AI10">
-        <v>0.5081223966677346</v>
+        <v>0.670488957394303</v>
       </c>
       <c r="AJ10">
-        <v>0.374934106483922</v>
+        <v>0.5550139455052563</v>
       </c>
       <c r="AK10">
-        <v>0.3934371172310245</v>
+        <v>0.6044149120101682</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1665,7 +1641,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alior Bank S.A. (WSE:ALR)</t>
+          <t>mBank S.A. (WSE:MBK)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1674,10 +1650,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.105</v>
-      </c>
-      <c r="E11">
-        <v>0.117</v>
+        <v>0.101</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1692,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>126.6</v>
+        <v>-640.2</v>
       </c>
       <c r="L11">
-        <v>0.1824733352551167</v>
+        <v>-0.4836808703535812</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1704,7 +1677,7 @@
         <v>-0</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1713,61 +1686,61 @@
         <v>-0</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>378.8</v>
+        <v>4139.7</v>
       </c>
       <c r="V11">
-        <v>0.2149463768938319</v>
+        <v>1.443108136373144</v>
       </c>
       <c r="W11">
-        <v>0.07557306590257878</v>
+        <v>-0.1537057933783103</v>
       </c>
       <c r="X11">
-        <v>0.05417869539853606</v>
+        <v>0.1060537334236563</v>
       </c>
       <c r="Y11">
-        <v>0.02139437050404273</v>
+        <v>-0.2597595268019666</v>
       </c>
       <c r="Z11">
-        <v>0.261850845410628</v>
+        <v>0.2365933136827654</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.04836256708636563</v>
+        <v>0.07772179552329589</v>
       </c>
       <c r="AC11">
-        <v>-0.04836256708636563</v>
+        <v>-0.07772179552329589</v>
       </c>
       <c r="AD11">
-        <v>797.6</v>
+        <v>3744.1</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>797.6</v>
+        <v>3744.1</v>
       </c>
       <c r="AG11">
-        <v>418.8</v>
+        <v>-395.5999999999999</v>
       </c>
       <c r="AH11">
-        <v>0.3115746708855814</v>
+        <v>0.5661983758525262</v>
       </c>
       <c r="AI11">
-        <v>0.3241749309055438</v>
+        <v>0.617481652510926</v>
       </c>
       <c r="AJ11">
-        <v>0.1920132043464307</v>
+        <v>-0.1599676506267691</v>
       </c>
       <c r="AK11">
-        <v>0.2011913912375096</v>
+        <v>-0.2056346813598086</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1784,7 +1757,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mBank S.A. (WSE:MBK)</t>
+          <t>Alior Bank S.A. (WSE:ALR)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1793,13 +1766,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.061</v>
+        <v>0.0317</v>
       </c>
       <c r="E12">
-        <v>-0.258</v>
-      </c>
-      <c r="F12">
-        <v>1.68</v>
+        <v>-0.08710000000000001</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1814,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>70</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L12">
-        <v>0.05137991779213153</v>
+        <v>0.136139008448908</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1841,176 +1811,60 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>4538.3</v>
+        <v>574.3</v>
       </c>
       <c r="V12">
-        <v>1.001566913841808</v>
+        <v>0.5620473673908788</v>
       </c>
       <c r="W12">
-        <v>0.01592320465867473</v>
+        <v>0.05135915323550638</v>
       </c>
       <c r="X12">
-        <v>0.07423635970763223</v>
+        <v>0.09560067900892996</v>
       </c>
       <c r="Y12">
-        <v>-0.0583131550489575</v>
+        <v>-0.04424152577342358</v>
       </c>
       <c r="Z12">
-        <v>0.1562706105955236</v>
+        <v>0.3013547271329746</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.04962713778276917</v>
+        <v>0.08109749455389789</v>
       </c>
       <c r="AC12">
-        <v>-0.04962713778276917</v>
+        <v>-0.08109749455389789</v>
       </c>
       <c r="AD12">
-        <v>5974.6</v>
+        <v>930.3</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>5974.6</v>
+        <v>930.3</v>
       </c>
       <c r="AG12">
-        <v>1436.3</v>
+        <v>356</v>
       </c>
       <c r="AH12">
-        <v>0.568695387309867</v>
+        <v>0.4765637006300907</v>
       </c>
       <c r="AI12">
-        <v>0.5891994240744759</v>
+        <v>0.4581404510981976</v>
       </c>
       <c r="AJ12">
-        <v>0.2406870548806033</v>
+        <v>0.2583829293075918</v>
       </c>
       <c r="AK12">
-        <v>0.2563951516449776</v>
+        <v>0.2444551260042574</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Getin Noble Bank S.A. (WSE:GNB)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>-0.115</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>-52</v>
-      </c>
-      <c r="L13">
-        <v>-0.385470719051149</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>706.7</v>
-      </c>
-      <c r="V13">
-        <v>8.433174224343675</v>
-      </c>
-      <c r="W13">
-        <v>-0.09379509379509379</v>
-      </c>
-      <c r="X13">
-        <v>0.1274728596753484</v>
-      </c>
-      <c r="Y13">
-        <v>-0.2212679534704422</v>
-      </c>
-      <c r="Z13">
-        <v>0.1507936507936508</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0.04993326632097785</v>
-      </c>
-      <c r="AC13">
-        <v>-0.04993326632097785</v>
-      </c>
-      <c r="AD13">
-        <v>303.1</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>303.1</v>
-      </c>
-      <c r="AG13">
-        <v>-403.6</v>
-      </c>
-      <c r="AH13">
-        <v>0.783406565003877</v>
-      </c>
-      <c r="AI13">
-        <v>0.3971956493251212</v>
-      </c>
-      <c r="AJ13">
-        <v>1.262038774233896</v>
-      </c>
-      <c r="AK13">
-        <v>-7.156028368794329</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/poland/poland_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08810000000000001</v>
+        <v>0.144</v>
       </c>
       <c r="E2">
-        <v>-0.00513</v>
+        <v>0.172</v>
       </c>
       <c r="F2">
-        <v>0.104</v>
+        <v>0.219</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>698.3</v>
+        <v>6315.01</v>
       </c>
       <c r="L2">
-        <v>0.05821980623968252</v>
+        <v>0.3274502991900609</v>
       </c>
       <c r="M2">
-        <v>1019.0924</v>
+        <v>675.6609999999999</v>
       </c>
       <c r="N2">
-        <v>0.03181601458596101</v>
+        <v>0.0108024352847694</v>
       </c>
       <c r="O2">
-        <v>1.459390519833882</v>
+        <v>0.1069928630358463</v>
       </c>
       <c r="P2">
-        <v>1019.0924</v>
+        <v>620.1</v>
       </c>
       <c r="Q2">
-        <v>0.03181601458596101</v>
+        <v>0.009914128712602183</v>
       </c>
       <c r="R2">
-        <v>1.459390519833882</v>
+        <v>0.09819461885254338</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>55.56099999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.08223206608047526</v>
       </c>
       <c r="U2">
-        <v>14961.2</v>
+        <v>12752.5</v>
       </c>
       <c r="V2">
-        <v>0.4670879278694257</v>
+        <v>0.2038863512457012</v>
       </c>
       <c r="W2">
-        <v>0.05016126698235721</v>
+        <v>0.2165947914513363</v>
       </c>
       <c r="X2">
-        <v>0.1045078533192682</v>
+        <v>0.07074264242014293</v>
       </c>
       <c r="Y2">
-        <v>-0.05434658633691103</v>
+        <v>0.1458521490311933</v>
       </c>
       <c r="Z2">
-        <v>0.1862189413208966</v>
+        <v>0.382374262346249</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07552540208701625</v>
+        <v>0.06211733129893054</v>
       </c>
       <c r="AC2">
-        <v>-0.07552540208701625</v>
+        <v>-0.06211733129893054</v>
       </c>
       <c r="AD2">
-        <v>38818.526</v>
+        <v>32974.397</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>38818.526</v>
+        <v>32974.397</v>
       </c>
       <c r="AG2">
-        <v>23857.326</v>
+        <v>20221.897</v>
       </c>
       <c r="AH2">
-        <v>0.5479025446198317</v>
+        <v>0.3452039387531793</v>
       </c>
       <c r="AI2">
-        <v>0.6083118804624587</v>
+        <v>0.457393308164289</v>
       </c>
       <c r="AJ2">
-        <v>0.4268764710414516</v>
+        <v>0.2443172894797794</v>
       </c>
       <c r="AK2">
-        <v>0.4883559894364088</v>
+        <v>0.3407830875276883</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -712,80 +712,101 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.311</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
       <c r="K3">
-        <v>-42.8</v>
+        <v>-2.99</v>
+      </c>
+      <c r="L3">
+        <v>-0.1633879781420765</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>2.294314381270903</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-22.94314381270903</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>25.2</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.842809364548495</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-8.42809364548495</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>43.39999999999999</v>
+      </c>
+      <c r="T3">
+        <v>0.6326530612244897</v>
       </c>
       <c r="U3">
-        <v>43.5</v>
+        <v>34.9</v>
       </c>
       <c r="V3">
-        <v>2.004608294930875</v>
+        <v>1.167224080267559</v>
       </c>
       <c r="W3">
-        <v>-0.2458357265939115</v>
+        <v>-0.06795454545454546</v>
       </c>
       <c r="X3">
-        <v>0.07164542988177777</v>
+        <v>0.06221303105042509</v>
       </c>
       <c r="Y3">
-        <v>-0.3174811564756893</v>
+        <v>-0.1301675765049705</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>29.23322683706081</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07155519558247968</v>
+        <v>0.06195354335807063</v>
       </c>
       <c r="AC3">
-        <v>-0.07155519558247968</v>
+        <v>-0.06195354335807063</v>
       </c>
       <c r="AD3">
-        <v>0.126</v>
+        <v>0.697</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.126</v>
+        <v>0.697</v>
       </c>
       <c r="AG3">
-        <v>-43.374</v>
+        <v>-34.203</v>
       </c>
       <c r="AH3">
-        <v>0.005772931366260423</v>
+        <v>0.02278001111220054</v>
       </c>
       <c r="AI3">
-        <v>0.00285545936635997</v>
+        <v>0.02856908636307743</v>
       </c>
       <c r="AJ3">
-        <v>2.001199593983574</v>
+        <v>7.94864048338369</v>
       </c>
       <c r="AK3">
-        <v>-69.2875399361025</v>
+        <v>3.256498143387604</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -811,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0929</v>
+        <v>0.148</v>
       </c>
       <c r="E4">
-        <v>0.0587</v>
+        <v>0.217</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -829,85 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>347</v>
+        <v>878.2</v>
       </c>
       <c r="L4">
-        <v>0.2612558349646137</v>
+        <v>0.4200306102927109</v>
       </c>
       <c r="M4">
-        <v>273.4</v>
+        <v>0.961</v>
       </c>
       <c r="N4">
-        <v>0.05583352053423734</v>
+        <v>0.0001134391784217671</v>
       </c>
       <c r="O4">
-        <v>0.7878962536023054</v>
+        <v>0.001094283762240947</v>
       </c>
       <c r="P4">
-        <v>273.4</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.05583352053423734</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.7878962536023054</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.961</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>378.1</v>
+        <v>221.1</v>
       </c>
       <c r="V4">
-        <v>0.07721526742500052</v>
+        <v>0.02609927403647524</v>
       </c>
       <c r="W4">
-        <v>0.07898031182428587</v>
+        <v>0.5855447392985732</v>
       </c>
       <c r="X4">
-        <v>0.08717260094146112</v>
+        <v>0.0672667266456472</v>
       </c>
       <c r="Y4">
-        <v>-0.008192289117175247</v>
+        <v>0.5182780126529261</v>
       </c>
       <c r="Z4">
-        <v>0.1904229390681004</v>
+        <v>0.5199184363654449</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07211964660397922</v>
+        <v>0.06195818958435417</v>
       </c>
       <c r="AC4">
-        <v>-0.07211964660397922</v>
+        <v>-0.06195818958435417</v>
       </c>
       <c r="AD4">
-        <v>2899.7</v>
+        <v>2497.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2899.7</v>
+        <v>2497.6</v>
       </c>
       <c r="AG4">
-        <v>2521.6</v>
+        <v>2276.5</v>
       </c>
       <c r="AH4">
-        <v>0.3719280693653481</v>
+        <v>0.2276941590467768</v>
       </c>
       <c r="AI4">
-        <v>0.6590976247300829</v>
+        <v>0.418127333299851</v>
       </c>
       <c r="AJ4">
-        <v>0.3399161532965774</v>
+        <v>0.2118068477856345</v>
       </c>
       <c r="AK4">
-        <v>0.627045307604317</v>
+        <v>0.3957616216404158</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -924,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Powszechna Kasa Oszczednosci Bank Polski Spólka Akcyjna (WSE:PKO)</t>
+          <t>Santander Bank Polska S.A. (WSE:SPL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -933,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0582</v>
+        <v>0.141</v>
       </c>
       <c r="E5">
-        <v>-0.00513</v>
+        <v>0.172</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -951,85 +972,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>566.6</v>
+        <v>1088.4</v>
       </c>
       <c r="L5">
-        <v>0.1994017244413162</v>
+        <v>0.3389281599352287</v>
       </c>
       <c r="M5">
-        <v>462.3</v>
+        <v>11.2</v>
       </c>
       <c r="N5">
-        <v>0.0534623924507355</v>
+        <v>0.0008797354509822402</v>
       </c>
       <c r="O5">
-        <v>0.8159195199435227</v>
+        <v>0.01029033443586916</v>
       </c>
       <c r="P5">
-        <v>462.3</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.0534623924507355</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.8159195199435227</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>2766.7</v>
+        <v>661</v>
       </c>
       <c r="V5">
-        <v>0.3199532796743454</v>
+        <v>0.05192010116957686</v>
       </c>
       <c r="W5">
-        <v>0.05413565443375405</v>
+        <v>0.1987255564279063</v>
       </c>
       <c r="X5">
-        <v>0.103141691316312</v>
+        <v>0.06958193300870806</v>
       </c>
       <c r="Y5">
-        <v>-0.04900603688255793</v>
+        <v>0.1291436234191983</v>
       </c>
       <c r="Z5">
-        <v>0.1340545181774435</v>
+        <v>0.2596521584449817</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0724109658954671</v>
+        <v>0.06201141687478366</v>
       </c>
       <c r="AC5">
-        <v>-0.0724109658954671</v>
+        <v>-0.06201141687478366</v>
       </c>
       <c r="AD5">
-        <v>10335.4</v>
+        <v>5337</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>10335.4</v>
+        <v>5337</v>
       </c>
       <c r="AG5">
-        <v>7568.7</v>
+        <v>4676</v>
       </c>
       <c r="AH5">
-        <v>0.5444670382350153</v>
+        <v>0.2953824696564664</v>
       </c>
       <c r="AI5">
-        <v>0.6174701134523817</v>
+        <v>0.3977463277215105</v>
       </c>
       <c r="AJ5">
-        <v>0.4667456015392299</v>
+        <v>0.2686260204169563</v>
       </c>
       <c r="AK5">
-        <v>0.5417203469896076</v>
+        <v>0.3665409850201065</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1046,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Santander Bank Polska S.A. (WSE:SPL)</t>
+          <t>Powszechna Kasa Oszczednosci Bank Polski Spólka Akcyjna (WSE:PKO)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1055,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.08810000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="E6">
-        <v>-0.00338</v>
+        <v>0.131</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1073,85 +1094,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>422.2</v>
+        <v>1502</v>
       </c>
       <c r="L6">
-        <v>0.1992731391891254</v>
+        <v>0.3287083643366744</v>
       </c>
       <c r="M6">
-        <v>55.3924</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.009149719193921374</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.1311994315490289</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>55.3924</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.009149719193921374</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.1311994315490289</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>623.9</v>
+        <v>3770.4</v>
       </c>
       <c r="V6">
-        <v>0.1030558308556326</v>
+        <v>0.2356647290455653</v>
       </c>
       <c r="W6">
-        <v>0.06143950638842807</v>
+        <v>0.2344640264747662</v>
       </c>
       <c r="X6">
-        <v>0.1058740153222245</v>
+        <v>0.07068211155339613</v>
       </c>
       <c r="Y6">
-        <v>-0.04443450893379643</v>
+        <v>0.1637819149213701</v>
       </c>
       <c r="Z6">
-        <v>0.18636255684467</v>
+        <v>0.3269742679680568</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07244549486119684</v>
+        <v>0.06203357080666388</v>
       </c>
       <c r="AC6">
-        <v>-0.07244549486119684</v>
+        <v>-0.06203357080666388</v>
       </c>
       <c r="AD6">
-        <v>7860.6</v>
+        <v>7652.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>7860.6</v>
+        <v>7652.6</v>
       </c>
       <c r="AG6">
-        <v>7236.700000000001</v>
+        <v>3882.2</v>
       </c>
       <c r="AH6">
-        <v>0.5649174248630935</v>
+        <v>0.3235552774442321</v>
       </c>
       <c r="AI6">
-        <v>0.5742232871408639</v>
+        <v>0.4240254882947777</v>
       </c>
       <c r="AJ6">
-        <v>0.5444935180238814</v>
+        <v>0.1952699032251574</v>
       </c>
       <c r="AK6">
-        <v>0.5538912530998378</v>
+        <v>0.2719179665338199</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1168,7 +1186,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bank Millennium S.A. (WSE:MIL)</t>
+          <t>Bank Handlowy w Warszawie S.A. (WSE:BHW)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1177,7 +1195,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.156</v>
+        <v>0.165</v>
+      </c>
+      <c r="E7">
+        <v>0.286</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1192,82 +1213,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-358.1</v>
+        <v>523.4</v>
       </c>
       <c r="L7">
-        <v>-0.3711265416105296</v>
+        <v>0.5050661005500338</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>269.2</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.07988367607347399</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>0.5143293847917463</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>269.2</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.07988367607347399</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>0.5143293847917463</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>2018.4</v>
+        <v>124.5</v>
       </c>
       <c r="V7">
-        <v>1.590669083458113</v>
+        <v>0.03694471646042909</v>
       </c>
       <c r="W7">
-        <v>-0.1781680680630877</v>
+        <v>0.3566852937167779</v>
       </c>
       <c r="X7">
-        <v>0.08801131286817385</v>
+        <v>0.07080317328688973</v>
       </c>
       <c r="Y7">
-        <v>-0.2661793809312616</v>
+        <v>0.2858821204298882</v>
       </c>
       <c r="Z7">
-        <v>0.4362904684391391</v>
+        <v>0.4725059274120008</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07453645262697177</v>
+        <v>0.06203590086524189</v>
       </c>
       <c r="AC7">
-        <v>-0.07453645262697177</v>
+        <v>-0.06203590086524189</v>
       </c>
       <c r="AD7">
-        <v>791.6</v>
+        <v>1633.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>791.6</v>
+        <v>1633.8</v>
       </c>
       <c r="AG7">
-        <v>-1226.8</v>
+        <v>1509.3</v>
       </c>
       <c r="AH7">
-        <v>0.3841785974278088</v>
+        <v>0.3265183764014629</v>
       </c>
       <c r="AI7">
-        <v>0.4460472192483236</v>
+        <v>0.4417347104309738</v>
       </c>
       <c r="AJ7">
-        <v>-29.14014251781479</v>
+        <v>0.3093334972946385</v>
       </c>
       <c r="AK7">
-        <v>5.034058268362738</v>
+        <v>0.422288128479897</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1293,7 +1317,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.08400000000000001</v>
+        <v>0.146</v>
+      </c>
+      <c r="E8">
+        <v>0.136</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1308,10 +1335,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>27.1</v>
+        <v>20.7</v>
       </c>
       <c r="L8">
-        <v>0.2135539795114263</v>
+        <v>0.100828056502679</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1335,55 +1362,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>43.5</v>
+        <v>40</v>
       </c>
       <c r="V8">
-        <v>0.2428810720268007</v>
+        <v>0.1506024096385542</v>
       </c>
       <c r="W8">
-        <v>0.0560264626834815</v>
+        <v>0.05318602261048304</v>
       </c>
       <c r="X8">
-        <v>0.1173109432693479</v>
+        <v>0.0830762871390168</v>
       </c>
       <c r="Y8">
-        <v>-0.06128448058586642</v>
+        <v>-0.02989026452853376</v>
       </c>
       <c r="Z8">
-        <v>0.1506589101270331</v>
+        <v>0.3131482611348384</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07651435154706071</v>
+        <v>0.06219876173261919</v>
       </c>
       <c r="AC8">
-        <v>-0.07651435154706071</v>
+        <v>-0.06219876173261919</v>
       </c>
       <c r="AD8">
-        <v>309.9</v>
+        <v>303.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>309.9</v>
+        <v>303.9</v>
       </c>
       <c r="AG8">
-        <v>266.4</v>
+        <v>263.9</v>
       </c>
       <c r="AH8">
-        <v>0.6337423312883436</v>
+        <v>0.5336259877085162</v>
       </c>
       <c r="AI8">
-        <v>0.4432842225718782</v>
+        <v>0.3850247054351957</v>
       </c>
       <c r="AJ8">
-        <v>0.5979797979797979</v>
+        <v>0.4983947119924457</v>
       </c>
       <c r="AK8">
-        <v>0.4063453325198292</v>
+        <v>0.3521953823568664</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1400,7 +1427,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BNP Paribas Bank Polska S.A. (WSE:BNP)</t>
+          <t>Bank Polska Kasa Opieki S.A. (WSE:PEO)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1409,7 +1436,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.149</v>
+        <v>0.142</v>
+      </c>
+      <c r="E9">
+        <v>0.172</v>
+      </c>
+      <c r="F9">
+        <v>0.219</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1424,82 +1457,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>-17.1</v>
+        <v>1314.4</v>
       </c>
       <c r="L9">
-        <v>-0.01807037937229209</v>
+        <v>0.4136975953669899</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>325.7</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.03208550881686533</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>0.2477936701156421</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>325.7</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.03208550881686533</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>0.2477936701156421</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>2227.5</v>
+        <v>1256.7</v>
       </c>
       <c r="V9">
-        <v>1.18006993006993</v>
+        <v>0.1238006107772633</v>
       </c>
       <c r="W9">
-        <v>-0.005569488323616585</v>
+        <v>0.3107034795763994</v>
       </c>
       <c r="X9">
-        <v>0.1182613938851505</v>
+        <v>0.07472983381035198</v>
       </c>
       <c r="Y9">
-        <v>-0.1238308822087671</v>
+        <v>0.2359736457660475</v>
       </c>
       <c r="Z9">
-        <v>0.1869493065707851</v>
+        <v>0.3012563409661974</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.076552015978465</v>
+        <v>0.06447672041671923</v>
       </c>
       <c r="AC9">
-        <v>-0.076552015978465</v>
+        <v>-0.06447672041671923</v>
       </c>
       <c r="AD9">
-        <v>3333.9</v>
+        <v>7062.9</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>3333.9</v>
+        <v>7062.9</v>
       </c>
       <c r="AG9">
-        <v>1106.4</v>
+        <v>5806.2</v>
       </c>
       <c r="AH9">
-        <v>0.6384946854352198</v>
+        <v>0.4103021395500148</v>
       </c>
       <c r="AI9">
-        <v>0.6029951708296407</v>
+        <v>0.5212587732569725</v>
       </c>
       <c r="AJ9">
-        <v>0.3695390781563127</v>
+        <v>0.3638608277141353</v>
       </c>
       <c r="AK9">
-        <v>0.335130550675471</v>
+        <v>0.4723175791100626</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1516,7 +1552,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bank Polska Kasa Opieki S.A. (WSE:PEO)</t>
+          <t>BNP Paribas Bank Polska S.A. (WSE:BNP)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1525,13 +1561,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0544</v>
+        <v>0.243</v>
       </c>
       <c r="E10">
-        <v>-0.0446</v>
-      </c>
-      <c r="F10">
-        <v>0.104</v>
+        <v>0.349</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1546,85 +1579,82 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>308.2</v>
+        <v>376.8</v>
       </c>
       <c r="L10">
-        <v>0.179520037278658</v>
+        <v>0.2284051645753774</v>
       </c>
       <c r="M10">
-        <v>228</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.04397130293913446</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.7397793640493187</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>228</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.04397130293913446</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.7397793640493187</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>2145.6</v>
+        <v>1889.7</v>
       </c>
       <c r="V10">
-        <v>0.4137931034482759</v>
+        <v>0.5877029296510543</v>
       </c>
       <c r="W10">
-        <v>0.04896338072920804</v>
+        <v>0.1716628701594533</v>
       </c>
       <c r="X10">
-        <v>0.1154768223111183</v>
+        <v>0.08009991275673711</v>
       </c>
       <c r="Y10">
-        <v>-0.0665134415819103</v>
+        <v>0.09156295740271619</v>
       </c>
       <c r="Z10">
-        <v>0.1918619595221332</v>
+        <v>0.4996970982007634</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07739945471849607</v>
+        <v>0.06450443686109585</v>
       </c>
       <c r="AC10">
-        <v>-0.07739945471849607</v>
+        <v>-0.06450443686109585</v>
       </c>
       <c r="AD10">
-        <v>8612.9</v>
+        <v>3164.9</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>8612.9</v>
+        <v>3164.9</v>
       </c>
       <c r="AG10">
-        <v>6467.299999999999</v>
+        <v>1275.2</v>
       </c>
       <c r="AH10">
-        <v>0.6242091302425696</v>
+        <v>0.4960425058382835</v>
       </c>
       <c r="AI10">
-        <v>0.670488957394303</v>
+        <v>0.5128749453078157</v>
       </c>
       <c r="AJ10">
-        <v>0.5550139455052563</v>
+        <v>0.2839709615641562</v>
       </c>
       <c r="AK10">
-        <v>0.6044149120101682</v>
+        <v>0.2978604129683267</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1641,7 +1671,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mBank S.A. (WSE:MBK)</t>
+          <t>Alior Bank S.A. (WSE:ALR)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1652,6 +1682,9 @@
       <c r="D11">
         <v>0.101</v>
       </c>
+      <c r="E11">
+        <v>0.222</v>
+      </c>
       <c r="G11">
         <v>0</v>
       </c>
@@ -1665,10 +1698,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>-640.2</v>
+        <v>412.9</v>
       </c>
       <c r="L11">
-        <v>-0.4836808703535812</v>
+        <v>0.3828465461288827</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1677,7 +1710,7 @@
         <v>-0</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1686,61 +1719,61 @@
         <v>-0</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>4139.7</v>
+        <v>582.4</v>
       </c>
       <c r="V11">
-        <v>1.443108136373144</v>
+        <v>0.2297435897435897</v>
       </c>
       <c r="W11">
-        <v>-0.1537057933783103</v>
+        <v>0.3752612923748069</v>
       </c>
       <c r="X11">
-        <v>0.1060537334236563</v>
+        <v>0.06905844245914175</v>
       </c>
       <c r="Y11">
-        <v>-0.2597595268019666</v>
+        <v>0.3062028499156652</v>
       </c>
       <c r="Z11">
-        <v>0.2365933136827654</v>
+        <v>0.7405754308864931</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07772179552329589</v>
+        <v>0.06454567559607904</v>
       </c>
       <c r="AC11">
-        <v>-0.07772179552329589</v>
+        <v>-0.06454567559607904</v>
       </c>
       <c r="AD11">
-        <v>3744.1</v>
+        <v>991.4</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>3744.1</v>
+        <v>991.4</v>
       </c>
       <c r="AG11">
-        <v>-395.5999999999999</v>
+        <v>409</v>
       </c>
       <c r="AH11">
-        <v>0.5661983758525262</v>
+        <v>0.2811365698729583</v>
       </c>
       <c r="AI11">
-        <v>0.617481652510926</v>
+        <v>0.3353175945342624</v>
       </c>
       <c r="AJ11">
-        <v>-0.1599676506267691</v>
+        <v>0.1389266304347826</v>
       </c>
       <c r="AK11">
-        <v>-0.2056346813598086</v>
+        <v>0.1722685536180608</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1757,7 +1790,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alior Bank S.A. (WSE:ALR)</t>
+          <t>mBank S.A. (WSE:MBK)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1766,10 +1799,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0317</v>
+        <v>0.172</v>
       </c>
       <c r="E12">
-        <v>-0.08710000000000001</v>
+        <v>-0.0765</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1784,10 +1817,10 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>85.40000000000001</v>
+        <v>201.2</v>
       </c>
       <c r="L12">
-        <v>0.136139008448908</v>
+        <v>0.0894778973583563</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1811,55 +1844,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>574.3</v>
+        <v>4171.8</v>
       </c>
       <c r="V12">
-        <v>0.5620473673908788</v>
+        <v>0.7219270770242443</v>
       </c>
       <c r="W12">
-        <v>0.05135915323550638</v>
+        <v>0.0867652766397861</v>
       </c>
       <c r="X12">
-        <v>0.09560067900892996</v>
+        <v>0.0757247151859169</v>
       </c>
       <c r="Y12">
-        <v>-0.04424152577342358</v>
+        <v>0.0110405614538692</v>
       </c>
       <c r="Z12">
-        <v>0.3013547271329746</v>
+        <v>1.172122602168474</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.08109749455389789</v>
+        <v>0.06505835461427828</v>
       </c>
       <c r="AC12">
-        <v>-0.08109749455389789</v>
+        <v>-0.06505835461427828</v>
       </c>
       <c r="AD12">
-        <v>930.3</v>
+        <v>4329.6</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>930.3</v>
+        <v>4329.6</v>
       </c>
       <c r="AG12">
-        <v>356</v>
+        <v>157.8000000000002</v>
       </c>
       <c r="AH12">
-        <v>0.4765637006300907</v>
+        <v>0.4283212805318403</v>
       </c>
       <c r="AI12">
-        <v>0.4581404510981976</v>
+        <v>0.5800953963234901</v>
       </c>
       <c r="AJ12">
-        <v>0.2583829293075918</v>
+        <v>0.0265813189589826</v>
       </c>
       <c r="AK12">
-        <v>0.2444551260042574</v>
+        <v>0.04793729874232948</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/research/traditional_assets/database/data/poland/poland_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.169</v>
+        <v>0.1495</v>
       </c>
       <c r="E2">
-        <v>0.232</v>
+        <v>0.191</v>
       </c>
       <c r="F2">
-        <v>-0.04480000000000001</v>
+        <v>0.1076</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2597.3</v>
+        <v>8101.47</v>
       </c>
       <c r="L2">
-        <v>0.3145421076852278</v>
+        <v>0.3219775371995422</v>
       </c>
       <c r="M2">
-        <v>1311.4</v>
+        <v>6037.24</v>
       </c>
       <c r="N2">
-        <v>0.07669005847953217</v>
+        <v>0.09617942157634306</v>
       </c>
       <c r="O2">
-        <v>0.5049089439032842</v>
+        <v>0.7452030310548579</v>
       </c>
       <c r="P2">
-        <v>1311.4</v>
+        <v>6015.5</v>
       </c>
       <c r="Q2">
-        <v>0.07669005847953217</v>
+        <v>0.09583308109210363</v>
       </c>
       <c r="R2">
-        <v>0.5049089439032842</v>
+        <v>0.7425195674365269</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>21.74000000000001</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.003600983230747827</v>
       </c>
       <c r="U2">
-        <v>8867.699999999999</v>
+        <v>21351.91</v>
       </c>
       <c r="V2">
-        <v>0.518578947368421</v>
+        <v>0.3401578127339869</v>
       </c>
       <c r="W2">
-        <v>0.2538825742971268</v>
+        <v>0.1842689838333615</v>
       </c>
       <c r="X2">
-        <v>0.08325193750348781</v>
+        <v>0.08039251300608513</v>
       </c>
       <c r="Y2">
-        <v>0.170630636793639</v>
+        <v>0.1038764708272764</v>
       </c>
       <c r="Z2">
-        <v>0.4600158772161947</v>
+        <v>0.4167859991336835</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06902214452442715</v>
+        <v>0.06809041589361331</v>
       </c>
       <c r="AC2">
-        <v>-0.06902214452442715</v>
+        <v>-0.06809041589361331</v>
       </c>
       <c r="AD2">
-        <v>14794.7</v>
+        <v>45434.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>14794.7</v>
+        <v>45434.9</v>
       </c>
       <c r="AG2">
-        <v>5927</v>
+        <v>24082.99</v>
       </c>
       <c r="AH2">
-        <v>0.4638607668358693</v>
+        <v>0.4198945524950211</v>
       </c>
       <c r="AI2">
-        <v>0.5003500322976662</v>
+        <v>0.4770869647394838</v>
       </c>
       <c r="AJ2">
-        <v>0.2573934945933035</v>
+        <v>0.2772826085830189</v>
       </c>
       <c r="AK2">
-        <v>0.2863146707888508</v>
+        <v>0.3259651967073482</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank Polska Kasa Opieki S.A. (WSE:PEO)</t>
+          <t>ING Bank Slaski S.A. (WSE:ING)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.141</v>
+        <v>0.148</v>
       </c>
       <c r="E3">
-        <v>0.232</v>
-      </c>
-      <c r="F3">
-        <v>-0.04480000000000001</v>
+        <v>0.211</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +731,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1646.2</v>
+        <v>1127.3</v>
       </c>
       <c r="L3">
-        <v>0.4243439707171212</v>
+        <v>0.423796992481203</v>
       </c>
       <c r="M3">
-        <v>1311.4</v>
+        <v>1132.34</v>
       </c>
       <c r="N3">
-        <v>0.1497459320582358</v>
+        <v>0.1489529071297027</v>
       </c>
       <c r="O3">
-        <v>0.796622524602114</v>
+        <v>1.004470859575978</v>
       </c>
       <c r="P3">
-        <v>1311.4</v>
+        <v>1129.4</v>
       </c>
       <c r="Q3">
-        <v>0.1497459320582358</v>
+        <v>0.148566166798211</v>
       </c>
       <c r="R3">
-        <v>0.796622524602114</v>
+        <v>1.001862858156658</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.940000000000055</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.002596393309430078</v>
       </c>
       <c r="U3">
-        <v>1674.6</v>
+        <v>2280.8</v>
       </c>
       <c r="V3">
-        <v>0.1912189551812732</v>
+        <v>0.3000263088660879</v>
       </c>
       <c r="W3">
-        <v>0.2538825742971268</v>
+        <v>0.324337543516414</v>
       </c>
       <c r="X3">
-        <v>0.08455249339627671</v>
+        <v>0.07968197863685719</v>
       </c>
       <c r="Y3">
-        <v>0.1693300809008501</v>
+        <v>0.2446555648795568</v>
       </c>
       <c r="Z3">
-        <v>0.3156472990895259</v>
+        <v>0.4624317652376483</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06814530241543396</v>
+        <v>0.0668195975859463</v>
       </c>
       <c r="AC3">
-        <v>-0.06814530241543396</v>
+        <v>-0.0668195975859463</v>
       </c>
       <c r="AD3">
-        <v>8674.799999999999</v>
+        <v>5410.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8674.799999999999</v>
+        <v>5410.3</v>
       </c>
       <c r="AG3">
-        <v>7000.199999999999</v>
+        <v>3129.5</v>
       </c>
       <c r="AH3">
-        <v>0.4976279664760244</v>
+        <v>0.4157835278928399</v>
       </c>
       <c r="AI3">
-        <v>0.5208494695318551</v>
+        <v>0.5615256875973015</v>
       </c>
       <c r="AJ3">
-        <v>0.4442399588772473</v>
+        <v>0.2916181335321251</v>
       </c>
       <c r="AK3">
-        <v>0.4672874737158305</v>
+        <v>0.4255391476979141</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alior Bank S.A. (WSE:ALR)</t>
+          <t>Santander Bank Polska S.A. (WSE:SPL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,10 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.169</v>
+        <v>0.151</v>
       </c>
       <c r="E4">
-        <v>0.42</v>
+        <v>0.171</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,82 +853,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>629.1</v>
+        <v>1374.3</v>
       </c>
       <c r="L4">
-        <v>0.4264217447298855</v>
+        <v>0.3372184325464985</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1824.5</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.1612561095251142</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>1.327584952339373</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>1805.7</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.1595944954614957</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>1.313905260860074</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>18.79999999999995</v>
+      </c>
+      <c r="T4">
+        <v>0.01030419292956972</v>
       </c>
       <c r="U4">
-        <v>452.9</v>
+        <v>347.7</v>
       </c>
       <c r="V4">
-        <v>0.1667525773195876</v>
+        <v>0.0307310218042654</v>
       </c>
       <c r="W4">
-        <v>0.3201200895583147</v>
+        <v>0.1798304153254298</v>
       </c>
       <c r="X4">
-        <v>0.07349987641713367</v>
+        <v>0.07897862695228614</v>
       </c>
       <c r="Y4">
-        <v>0.246620213141181</v>
+        <v>0.1008517883731437</v>
       </c>
       <c r="Z4">
-        <v>0.6213882570971275</v>
+        <v>0.3417153685552099</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06902214452442715</v>
+        <v>0.0668356531141729</v>
       </c>
       <c r="AC4">
-        <v>-0.06902214452442715</v>
+        <v>-0.0668356531141729</v>
       </c>
       <c r="AD4">
-        <v>966.7</v>
+        <v>7595.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>966.7</v>
+        <v>7595.2</v>
       </c>
       <c r="AG4">
-        <v>513.8000000000001</v>
+        <v>7247.5</v>
       </c>
       <c r="AH4">
-        <v>0.2624976240258506</v>
+        <v>0.4016605409979111</v>
       </c>
       <c r="AI4">
-        <v>0.2564122967560542</v>
+        <v>0.4623663768962915</v>
       </c>
       <c r="AJ4">
-        <v>0.1590810576506285</v>
+        <v>0.3904524345699232</v>
       </c>
       <c r="AK4">
-        <v>0.1548896659833595</v>
+        <v>0.4507404021369355</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,114 +948,965 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Bank Handlowy w Warszawie S.A. (WSE:BHW)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.171</v>
+      </c>
+      <c r="E5">
+        <v>0.321</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>479.5</v>
+      </c>
+      <c r="L5">
+        <v>0.429967718794835</v>
+      </c>
+      <c r="M5">
+        <v>378.7</v>
+      </c>
+      <c r="N5">
+        <v>0.1352306813312384</v>
+      </c>
+      <c r="O5">
+        <v>0.7897810218978102</v>
+      </c>
+      <c r="P5">
+        <v>378.7</v>
+      </c>
+      <c r="Q5">
+        <v>0.1352306813312384</v>
+      </c>
+      <c r="R5">
+        <v>0.7897810218978102</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>506.3</v>
+      </c>
+      <c r="V5">
+        <v>0.1807956006284817</v>
+      </c>
+      <c r="W5">
+        <v>0.2322258814413018</v>
+      </c>
+      <c r="X5">
+        <v>0.07807793805830676</v>
+      </c>
+      <c r="Y5">
+        <v>0.154147943382995</v>
+      </c>
+      <c r="Z5">
+        <v>0.3120226070898968</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.06685738300525815</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06685738300525815</v>
+      </c>
+      <c r="AD5">
+        <v>1735</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1735</v>
+      </c>
+      <c r="AG5">
+        <v>1228.7</v>
+      </c>
+      <c r="AH5">
+        <v>0.3825461921770958</v>
+      </c>
+      <c r="AI5">
+        <v>0.4052602074184808</v>
+      </c>
+      <c r="AJ5">
+        <v>0.3049564418852845</v>
+      </c>
+      <c r="AK5">
+        <v>0.3254920660149938</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Powszechna Kasa Oszczednosci Bank Polski Spólka Akcyjna (WSE:PKO)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.0978</v>
+      </c>
+      <c r="E6">
+        <v>0.118</v>
+      </c>
+      <c r="F6">
+        <v>0.26</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1962.2</v>
+      </c>
+      <c r="L6">
+        <v>0.3662255734522855</v>
+      </c>
+      <c r="M6">
+        <v>1259.1</v>
+      </c>
+      <c r="N6">
+        <v>0.06966360517870974</v>
+      </c>
+      <c r="O6">
+        <v>0.6416777086943226</v>
+      </c>
+      <c r="P6">
+        <v>1259.1</v>
+      </c>
+      <c r="Q6">
+        <v>0.06966360517870974</v>
+      </c>
+      <c r="R6">
+        <v>0.6416777086943226</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>5131.2</v>
+      </c>
+      <c r="V6">
+        <v>0.2838995241783778</v>
+      </c>
+      <c r="W6">
+        <v>0.1887075523412931</v>
+      </c>
+      <c r="X6">
+        <v>0.07615297325565427</v>
+      </c>
+      <c r="Y6">
+        <v>0.1125545790856388</v>
+      </c>
+      <c r="Z6">
+        <v>0.3751951989804135</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06786506702260016</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06786506702260016</v>
+      </c>
+      <c r="AD6">
+        <v>9199.299999999999</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>9199.299999999999</v>
+      </c>
+      <c r="AG6">
+        <v>4068.099999999999</v>
+      </c>
+      <c r="AH6">
+        <v>0.3373005833544162</v>
+      </c>
+      <c r="AI6">
+        <v>0.4119612189606144</v>
+      </c>
+      <c r="AJ6">
+        <v>0.1837269274368736</v>
+      </c>
+      <c r="AK6">
+        <v>0.2365270679620682</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bank Millennium S.A. (WSE:MIL)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.158</v>
+      </c>
+      <c r="E7">
+        <v>-0.0237</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>172.3</v>
+      </c>
+      <c r="L7">
+        <v>0.1091611758743031</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>-0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>1833.6</v>
+      </c>
+      <c r="V7">
+        <v>0.7019101940818435</v>
+      </c>
+      <c r="W7">
+        <v>0.1132435096943806</v>
+      </c>
+      <c r="X7">
+        <v>0.08110304737531308</v>
+      </c>
+      <c r="Y7">
+        <v>0.03214046231906748</v>
+      </c>
+      <c r="Z7">
+        <v>0.8500188486186655</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.06804350266858353</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06804350266858353</v>
+      </c>
+      <c r="AD7">
+        <v>2072.4</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>2072.4</v>
+      </c>
+      <c r="AG7">
+        <v>238.8000000000002</v>
+      </c>
+      <c r="AH7">
+        <v>0.442376246077657</v>
+      </c>
+      <c r="AI7">
+        <v>0.5101292307692308</v>
+      </c>
+      <c r="AJ7">
+        <v>0.08375714636456109</v>
+      </c>
+      <c r="AK7">
+        <v>0.1071380501592715</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bank Polska Kasa Opieki S.A. (WSE:PEO)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.141</v>
+      </c>
+      <c r="E8">
+        <v>0.232</v>
+      </c>
+      <c r="F8">
+        <v>-0.04480000000000001</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1646.2</v>
+      </c>
+      <c r="L8">
+        <v>0.4243439707171212</v>
+      </c>
+      <c r="M8">
+        <v>1311.4</v>
+      </c>
+      <c r="N8">
+        <v>0.1497459320582358</v>
+      </c>
+      <c r="O8">
+        <v>0.796622524602114</v>
+      </c>
+      <c r="P8">
+        <v>1311.4</v>
+      </c>
+      <c r="Q8">
+        <v>0.1497459320582358</v>
+      </c>
+      <c r="R8">
+        <v>0.796622524602114</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>1674.6</v>
+      </c>
+      <c r="V8">
+        <v>0.1912189551812732</v>
+      </c>
+      <c r="W8">
+        <v>0.2538825742971268</v>
+      </c>
+      <c r="X8">
+        <v>0.08453662209720191</v>
+      </c>
+      <c r="Y8">
+        <v>0.1693459521999249</v>
+      </c>
+      <c r="Z8">
+        <v>0.3156472990895259</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.06813732911864308</v>
+      </c>
+      <c r="AC8">
+        <v>-0.06813732911864308</v>
+      </c>
+      <c r="AD8">
+        <v>8674.799999999999</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>8674.799999999999</v>
+      </c>
+      <c r="AG8">
+        <v>7000.199999999999</v>
+      </c>
+      <c r="AH8">
+        <v>0.4976279664760244</v>
+      </c>
+      <c r="AI8">
+        <v>0.5208494695318551</v>
+      </c>
+      <c r="AJ8">
+        <v>0.4442399588772473</v>
+      </c>
+      <c r="AK8">
+        <v>0.4672874737158305</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bank Ochrony Srodowiska S.A. (WSE:BOS)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0922</v>
+      </c>
+      <c r="E9">
+        <v>-0.198</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>6.27</v>
+      </c>
+      <c r="L9">
+        <v>0.03265625</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>-0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>7.71</v>
+      </c>
+      <c r="V9">
+        <v>0.03491847826086956</v>
+      </c>
+      <c r="W9">
+        <v>0.01291718170580964</v>
+      </c>
+      <c r="X9">
+        <v>0.08709787462146518</v>
+      </c>
+      <c r="Y9">
+        <v>-0.07418069291565553</v>
+      </c>
+      <c r="Z9">
+        <v>0.2562391565461097</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.0681960438375562</v>
+      </c>
+      <c r="AC9">
+        <v>-0.0681960438375562</v>
+      </c>
+      <c r="AD9">
+        <v>251.2</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>251.2</v>
+      </c>
+      <c r="AG9">
+        <v>243.49</v>
+      </c>
+      <c r="AH9">
+        <v>0.5322033898305084</v>
+      </c>
+      <c r="AI9">
+        <v>0.3033083796184496</v>
+      </c>
+      <c r="AJ9">
+        <v>0.5244351590600702</v>
+      </c>
+      <c r="AK9">
+        <v>0.296761691184536</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BNP Paribas Bank Polska S.A. (WSE:BNP)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.148</v>
+      </c>
+      <c r="E10">
+        <v>0.224</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>382.3</v>
+      </c>
+      <c r="L10">
+        <v>0.1985664571755051</v>
+      </c>
+      <c r="M10">
+        <v>131.2</v>
+      </c>
+      <c r="N10">
+        <v>0.04306157279768937</v>
+      </c>
+      <c r="O10">
+        <v>0.343185979597175</v>
+      </c>
+      <c r="P10">
+        <v>131.2</v>
+      </c>
+      <c r="Q10">
+        <v>0.04306157279768937</v>
+      </c>
+      <c r="R10">
+        <v>0.343185979597175</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>2376.9</v>
+      </c>
+      <c r="V10">
+        <v>0.7801299724300905</v>
+      </c>
+      <c r="W10">
+        <v>0.1271789753825682</v>
+      </c>
+      <c r="X10">
+        <v>0.09230034531948356</v>
+      </c>
+      <c r="Y10">
+        <v>0.03487863006308464</v>
+      </c>
+      <c r="Z10">
+        <v>0.4497103615808652</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.06829347730503849</v>
+      </c>
+      <c r="AC10">
+        <v>-0.06829347730503849</v>
+      </c>
+      <c r="AD10">
+        <v>4376.8</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>4376.8</v>
+      </c>
+      <c r="AG10">
+        <v>1999.9</v>
+      </c>
+      <c r="AH10">
+        <v>0.5895791799127108</v>
+      </c>
+      <c r="AI10">
+        <v>0.5402723086988187</v>
+      </c>
+      <c r="AJ10">
+        <v>0.3962787564150831</v>
+      </c>
+      <c r="AK10">
+        <v>0.3493763320638691</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alior Bank S.A. (WSE:ALR)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.169</v>
+      </c>
+      <c r="E11">
+        <v>0.42</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>629.1</v>
+      </c>
+      <c r="L11">
+        <v>0.4264217447298855</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>-0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>-0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>452.9</v>
+      </c>
+      <c r="V11">
+        <v>0.1667525773195876</v>
+      </c>
+      <c r="W11">
+        <v>0.3201200895583147</v>
+      </c>
+      <c r="X11">
+        <v>0.07348853177877826</v>
+      </c>
+      <c r="Y11">
+        <v>0.2466315577795364</v>
+      </c>
+      <c r="Z11">
+        <v>0.6213882570971275</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.06901377782668547</v>
+      </c>
+      <c r="AC11">
+        <v>-0.06901377782668547</v>
+      </c>
+      <c r="AD11">
+        <v>966.7</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>966.7</v>
+      </c>
+      <c r="AG11">
+        <v>513.8000000000001</v>
+      </c>
+      <c r="AH11">
+        <v>0.2624976240258506</v>
+      </c>
+      <c r="AI11">
+        <v>0.2564122967560542</v>
+      </c>
+      <c r="AJ11">
+        <v>0.1590810576506285</v>
+      </c>
+      <c r="AK11">
+        <v>0.1548896659833595</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>mBank S.A. (WSE:MBK)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D12">
         <v>0.186</v>
       </c>
-      <c r="E5">
+      <c r="E12">
         <v>0.0061</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
         <v>322</v>
       </c>
-      <c r="L5">
+      <c r="L12">
         <v>0.1109312019843594</v>
       </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
+      <c r="M12">
+        <v>-0</v>
+      </c>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>-0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>-0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
         <v>6740.2</v>
       </c>
-      <c r="V5">
+      <c r="V12">
         <v>1.197938327557096</v>
       </c>
-      <c r="W5">
+      <c r="W12">
         <v>0.10276049146322</v>
       </c>
-      <c r="X5">
-        <v>0.08325193750348781</v>
-      </c>
-      <c r="Y5">
-        <v>0.01950855395973224</v>
-      </c>
-      <c r="Z5">
+      <c r="X12">
+        <v>0.08323659885430798</v>
+      </c>
+      <c r="Y12">
+        <v>0.01952389260891206</v>
+      </c>
+      <c r="Z12">
         <v>0.8834208323822567</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.06908012755027543</v>
-      </c>
-      <c r="AC5">
-        <v>-0.06908012755027543</v>
-      </c>
-      <c r="AD5">
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.0690721214917014</v>
+      </c>
+      <c r="AC12">
+        <v>-0.0690721214917014</v>
+      </c>
+      <c r="AD12">
         <v>5153.2</v>
       </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
         <v>5153.2</v>
       </c>
-      <c r="AG5">
+      <c r="AG12">
         <v>-1587</v>
       </c>
-      <c r="AH5">
+      <c r="AH12">
         <v>0.4780466988877241</v>
       </c>
-      <c r="AI5">
+      <c r="AI12">
         <v>0.5635916224640455</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ12">
         <v>-0.3928704047530635</v>
       </c>
-      <c r="AK5">
+      <c r="AK12">
         <v>-0.6603420297091499</v>
       </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
         <v>0</v>
       </c>
     </row>
